--- a/data/trans_orig/IQ27A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ27A-Edad-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Talla media, en centímetros, referida por progenitor/a</t>
+          <t>Talla media, en centímetros, declarada por progenitor/a (tasa de respuesta: 90,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>73,63; 78,28</t>
+          <t>73,46; 78,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>71,08; 75,15</t>
+          <t>71,14; 75,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>72,65; 76,45</t>
+          <t>72,57; 76,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>86,05; 96,53</t>
+          <t>86,12; 96,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>74,37; 79,4</t>
+          <t>74,48; 79,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,97; 77,3</t>
+          <t>72,94; 77,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,61; 79,99</t>
+          <t>75,46; 79,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>81,46; 90,57</t>
+          <t>81,55; 90,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>74,83; 78,33</t>
+          <t>74,69; 78,2</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>72,72; 75,51</t>
+          <t>72,5; 75,52</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>74,64; 77,44</t>
+          <t>74,57; 77,44</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>84,97; 91,82</t>
+          <t>84,94; 91,7</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>109,46; 112,59</t>
+          <t>109,46; 112,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>108,66; 111,42</t>
+          <t>108,74; 111,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>109,78; 112,8</t>
+          <t>109,85; 113,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>111,22; 117,26</t>
+          <t>111,29; 117,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>110,09; 113,18</t>
+          <t>110,1; 113,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>107,18; 110,37</t>
+          <t>107,26; 110,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>109,14; 112,5</t>
+          <t>109,18; 112,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>116,85; 122,65</t>
+          <t>116,69; 122,27</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>110,31; 112,44</t>
+          <t>110,22; 112,29</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>108,36; 110,49</t>
+          <t>108,32; 110,43</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>109,75; 112,15</t>
+          <t>109,88; 112,13</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>115,28; 119,31</t>
+          <t>115,26; 119,39</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>138,93; 142,31</t>
+          <t>139,0; 142,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>134,93; 138,41</t>
+          <t>134,8; 138,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>136,12; 139,18</t>
+          <t>136,06; 139,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>134,44; 140,13</t>
+          <t>134,25; 140,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>139,05; 142,4</t>
+          <t>139,07; 142,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>134,38; 137,91</t>
+          <t>134,19; 137,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>136,81; 139,58</t>
+          <t>136,97; 139,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>135,63; 141,07</t>
+          <t>136,32; 141,18</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>139,54; 141,79</t>
+          <t>139,6; 141,91</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>135,24; 137,72</t>
+          <t>135,0; 137,72</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>136,88; 138,89</t>
+          <t>136,97; 139,0</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>136,0; 139,88</t>
+          <t>136,11; 139,97</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>157,62; 159,57</t>
+          <t>157,65; 159,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>155,79; 158,5</t>
+          <t>155,73; 158,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>156,17; 158,78</t>
+          <t>156,2; 158,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>145,27; 153,25</t>
+          <t>145,41; 153,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>163,49; 165,95</t>
+          <t>163,36; 165,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>160,34; 163,6</t>
+          <t>160,35; 163,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>159,75; 163,12</t>
+          <t>159,9; 163,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>152,87; 158,73</t>
+          <t>152,77; 158,21</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>160,94; 162,58</t>
+          <t>160,94; 162,61</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>158,55; 160,77</t>
+          <t>158,63; 160,69</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>158,55; 160,62</t>
+          <t>158,56; 160,64</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>150,17; 155,05</t>
+          <t>150,36; 155,01</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>124,21; 128,03</t>
+          <t>124,21; 128,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>119,23; 123,39</t>
+          <t>119,47; 123,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>121,04; 125,13</t>
+          <t>121,09; 125,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>131,21; 137,15</t>
+          <t>131,05; 137,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>125,69; 129,42</t>
+          <t>125,39; 129,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>120,6; 124,97</t>
+          <t>120,89; 125,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>122,47; 126,53</t>
+          <t>122,44; 126,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>134,73; 139,46</t>
+          <t>134,57; 139,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>125,5; 128,29</t>
+          <t>125,42; 128,28</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>120,65; 123,68</t>
+          <t>120,6; 123,63</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>122,35; 125,16</t>
+          <t>122,48; 125,23</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>133,61; 137,29</t>
+          <t>133,66; 137,31</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ27A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ27A-Edad-trans_orig.xlsx
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>73,46; 78,12</t>
+          <t>73,61; 78,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>71,14; 75,11</t>
+          <t>71,1; 74,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>72,57; 76,51</t>
+          <t>72,73; 76,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>86,12; 96,73</t>
+          <t>86,02; 96,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>74,48; 79,39</t>
+          <t>74,66; 79,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,94; 77,53</t>
+          <t>72,94; 77,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,46; 79,94</t>
+          <t>75,66; 79,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>81,55; 90,36</t>
+          <t>81,52; 90,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>74,69; 78,2</t>
+          <t>74,65; 78,31</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>72,5; 75,52</t>
+          <t>72,5; 75,38</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>74,57; 77,44</t>
+          <t>74,56; 77,43</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>84,94; 91,7</t>
+          <t>84,77; 91,55</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>109,46; 112,54</t>
+          <t>109,59; 112,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>108,74; 111,59</t>
+          <t>108,65; 111,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>109,85; 113,0</t>
+          <t>109,86; 113,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>111,29; 117,38</t>
+          <t>111,22; 117,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>110,1; 113,13</t>
+          <t>110,16; 113,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>107,26; 110,39</t>
+          <t>107,23; 110,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>109,18; 112,29</t>
+          <t>108,96; 112,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>116,69; 122,27</t>
+          <t>116,8; 122,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>110,22; 112,29</t>
+          <t>110,16; 112,3</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>108,32; 110,43</t>
+          <t>108,36; 110,58</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>109,88; 112,13</t>
+          <t>109,73; 112,12</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>115,26; 119,39</t>
+          <t>115,16; 119,21</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>139,0; 142,19</t>
+          <t>139,11; 142,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>134,8; 138,22</t>
+          <t>134,89; 138,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>136,06; 139,04</t>
+          <t>136,15; 139,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>134,25; 140,25</t>
+          <t>134,11; 139,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>139,07; 142,23</t>
+          <t>139,1; 142,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>134,19; 137,9</t>
+          <t>134,34; 138,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>136,97; 139,56</t>
+          <t>136,89; 139,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>136,32; 141,18</t>
+          <t>136,07; 141,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>139,6; 141,91</t>
+          <t>139,53; 141,97</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>135,0; 137,72</t>
+          <t>135,08; 137,62</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>136,97; 139,0</t>
+          <t>136,95; 139,08</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>136,11; 139,97</t>
+          <t>135,98; 139,96</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>157,65; 159,61</t>
+          <t>157,7; 159,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>155,73; 158,51</t>
+          <t>155,86; 158,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>156,2; 158,93</t>
+          <t>156,19; 158,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>145,41; 153,19</t>
+          <t>145,32; 153,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>163,36; 165,89</t>
+          <t>163,53; 165,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>160,35; 163,47</t>
+          <t>160,39; 163,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>159,9; 163,29</t>
+          <t>159,96; 163,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>152,77; 158,21</t>
+          <t>152,91; 158,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>160,94; 162,61</t>
+          <t>160,85; 162,51</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>158,63; 160,69</t>
+          <t>158,62; 160,72</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>158,56; 160,64</t>
+          <t>158,45; 160,56</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>150,36; 155,01</t>
+          <t>150,31; 155,18</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>124,21; 128,07</t>
+          <t>124,07; 128,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>119,47; 123,72</t>
+          <t>119,31; 123,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>121,09; 125,16</t>
+          <t>121,11; 124,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>131,05; 137,31</t>
+          <t>131,1; 137,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>125,39; 129,53</t>
+          <t>125,48; 129,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>120,89; 125,19</t>
+          <t>120,66; 124,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>122,44; 126,57</t>
+          <t>122,5; 126,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>134,57; 139,15</t>
+          <t>134,74; 139,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>125,42; 128,28</t>
+          <t>125,32; 128,2</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>120,6; 123,63</t>
+          <t>120,75; 123,51</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>122,48; 125,23</t>
+          <t>122,25; 125,1</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>133,66; 137,31</t>
+          <t>133,62; 137,31</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ27A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ27A-Edad-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>76,88</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>75,13</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>77,61</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>85,45</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>75,97</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>73,03</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>74,6</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>90,63</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>76,88</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>75,13</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>77,61</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>85,55</t>
+          <t>91,65</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>88,04</t>
+          <t>88,64</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>73,61; 78,51</t>
+          <t>74,37; 79,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>71,1; 74,96</t>
+          <t>72,97; 77,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>72,73; 76,47</t>
+          <t>75,61; 79,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>86,02; 96,61</t>
+          <t>81,54; 90,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>74,66; 79,57</t>
+          <t>73,63; 78,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,94; 77,33</t>
+          <t>71,08; 75,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,66; 79,72</t>
+          <t>72,65; 76,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>81,52; 90,15</t>
+          <t>86,73; 97,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>74,65; 78,31</t>
+          <t>74,83; 78,33</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>72,5; 75,38</t>
+          <t>72,72; 75,51</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>74,56; 77,43</t>
+          <t>74,64; 77,44</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>84,77; 91,55</t>
+          <t>85,45; 92,48</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>111,66</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>108,97</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>110,64</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>120,02</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>110,96</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>110,09</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>111,37</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>114,59</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>111,66</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>108,97</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>110,64</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>119,6</t>
+          <t>115,65</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>117,35</t>
+          <t>117,98</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>109,59; 112,61</t>
+          <t>110,09; 113,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>108,65; 111,52</t>
+          <t>107,18; 110,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>109,86; 113,0</t>
+          <t>109,14; 112,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>111,22; 117,01</t>
+          <t>117,26; 123,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>110,16; 113,29</t>
+          <t>109,46; 112,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>107,23; 110,58</t>
+          <t>108,66; 111,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>108,96; 112,29</t>
+          <t>109,78; 112,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>116,8; 122,66</t>
+          <t>112,94; 118,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>110,16; 112,3</t>
+          <t>110,31; 112,44</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>108,36; 110,58</t>
+          <t>108,36; 110,49</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>109,73; 112,12</t>
+          <t>109,75; 112,15</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>115,16; 119,21</t>
+          <t>116,08; 119,91</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>140,75</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>136,28</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>138,27</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>139,0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>140,68</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>136,66</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>137,63</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>137,13</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>140,75</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>136,28</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>138,27</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>138,72</t>
+          <t>136,73</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>137,99</t>
+          <t>137,93</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>139,11; 142,36</t>
+          <t>139,05; 142,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>134,89; 138,59</t>
+          <t>134,38; 137,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>136,15; 139,05</t>
+          <t>136,81; 139,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>134,11; 139,93</t>
+          <t>135,99; 141,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>139,1; 142,28</t>
+          <t>138,93; 142,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>134,34; 138,07</t>
+          <t>134,93; 138,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>136,89; 139,65</t>
+          <t>136,12; 139,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>136,07; 141,4</t>
+          <t>134,15; 139,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>139,53; 141,97</t>
+          <t>139,54; 141,79</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>135,08; 137,62</t>
+          <t>135,24; 137,72</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>136,95; 139,08</t>
+          <t>136,88; 138,89</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>135,98; 139,96</t>
+          <t>136,0; 139,65</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>164,63</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>162,04</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>161,59</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>155,37</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>158,72</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>157,29</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>157,6</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>150,15</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>164,63</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>162,04</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>161,59</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>155,56</t>
+          <t>150,86</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>153,01</t>
+          <t>153,29</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>157,7; 159,61</t>
+          <t>163,49; 165,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>155,86; 158,6</t>
+          <t>160,34; 163,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>156,19; 158,83</t>
+          <t>159,75; 163,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>145,32; 153,4</t>
+          <t>152,84; 157,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>163,53; 165,82</t>
+          <t>157,62; 159,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>160,39; 163,64</t>
+          <t>155,79; 158,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>159,96; 163,21</t>
+          <t>156,17; 158,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>152,91; 158,25</t>
+          <t>148,21; 152,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>160,85; 162,51</t>
+          <t>160,94; 162,58</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>158,62; 160,72</t>
+          <t>158,55; 160,77</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>158,45; 160,56</t>
+          <t>158,55; 160,62</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>150,31; 155,18</t>
+          <t>151,68; 154,96</t>
         </is>
       </c>
     </row>
@@ -1208,42 +1208,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>127,6</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>122,81</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>124,47</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>137,89</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>126,08</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>121,45</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>123,11</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>133,48</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>127,6</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>122,81</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>124,47</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>136,87</t>
+          <t>134,06</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>135,29</t>
+          <t>136,09</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>124,07; 128,06</t>
+          <t>125,69; 129,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>119,31; 123,53</t>
+          <t>120,6; 124,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>121,11; 124,97</t>
+          <t>122,47; 126,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>131,1; 137,36</t>
+          <t>135,81; 140,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>125,48; 129,75</t>
+          <t>124,21; 128,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>120,66; 124,97</t>
+          <t>119,23; 123,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>122,5; 126,43</t>
+          <t>121,04; 125,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>134,74; 139,18</t>
+          <t>132,4; 135,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>125,32; 128,2</t>
+          <t>125,5; 128,29</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>120,75; 123,51</t>
+          <t>120,65; 123,68</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>122,25; 125,1</t>
+          <t>122,35; 125,16</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>133,62; 137,31</t>
+          <t>134,74; 137,44</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ27A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ27A-Edad-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -526,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Talla media, en centímetros, declarada por progenitor/a (tasa de respuesta: 90,55%)</t>
+          <t>Talla media, en centímetros, declarada por madres/padres (tasa de respuesta: 90,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -646,419 +651,271 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>76,88</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>75,13</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>77,61</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>85,45</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>75,97</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>73,03</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>74,6</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>91,65</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>76,47</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>74,07</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>76,05</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>88,64</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>76.88498563501003</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>75.13266080173258</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>77.61115024373292</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>85.44629042586628</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>75.97099048544985</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>73.03477103015052</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>74.59862586119679</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>91.65472648982535</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>76.47082456106651</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>74.06584961659745</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>76.05021115539485</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>88.63936181814218</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>74,37; 79,4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>72,97; 77,3</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>75,61; 79,99</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>81,54; 90,2</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>73,63; 78,28</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>71,08; 75,15</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>72,65; 76,45</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>86,73; 97,49</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>74,83; 78,33</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>72,72; 75,51</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>74,64; 77,44</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>85,45; 92,48</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>74.37200493287698</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>72.97120238711462</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>75.60715629893467</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>81.53949786175227</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>73.63435725670358</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>71.0848932034356</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>72.64559794341562</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>86.73335489272647</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>74.8280340867236</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>72.72272877528873</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>74.6404827981557</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>85.4509680909989</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>79.40299831451229</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>77.2986460498081</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>79.98862016150548</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>90.19546013255436</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>78.27970073656041</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>75.1541649924246</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>76.45343168611629</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>97.48998480988756</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>78.33312368274186</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>75.50602162282641</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>77.43903840398126</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>92.48370524752536</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>111,66</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>108,97</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>110,64</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>120,02</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>110,96</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>110,09</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>111,37</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>115,65</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>111,31</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>109,49</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>110,97</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>117,98</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>110,09; 113,18</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>107,18; 110,37</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>109,14; 112,5</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>117,26; 123,1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>109,46; 112,59</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>108,66; 111,42</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>109,78; 112,8</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>112,94; 118,13</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>110,31; 112,44</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>108,36; 110,49</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>109,75; 112,15</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>116,08; 119,91</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>111.6556082603724</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>108.9658608320491</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>110.6393911234513</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>120.0156192757188</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>110.9626717643881</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>110.0864182085013</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>111.3658287968826</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>115.6462777790367</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>111.3084305991995</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>109.4907239255459</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>110.9665262408147</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>117.9773263982037</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>140,75</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>136,28</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>138,27</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>139,0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>140,68</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>136,66</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>137,63</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>136,73</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>140,72</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>136,47</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>137,95</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>137,93</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>110.09171236641</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>107.1828797794428</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>109.1365590452022</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>117.257311736111</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>109.4625175871278</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>108.6634005442956</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>109.7774497738063</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>112.9428213344344</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>110.3136341689076</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>108.3599110601272</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>109.753605938992</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>116.076524747764</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>139,05; 142,4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>134,38; 137,91</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>136,81; 139,58</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>135,99; 141,42</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>138,93; 142,31</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>134,93; 138,41</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>136,12; 139,18</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>134,15; 139,27</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>139,54; 141,79</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>135,24; 137,72</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>136,88; 138,89</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>136,0; 139,65</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>113.1796208985486</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>110.366694867154</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>112.5018795703516</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>123.1038793886899</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>112.5932940434835</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>111.4177104918035</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>112.7982096055103</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>118.1260410301023</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>112.4448207716603</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>110.4903277179143</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>112.1532741495257</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>119.9068795808819</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,277 +923,405 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>164,63</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>162,04</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>161,59</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>155,37</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>158,72</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>157,29</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>157,6</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>150,86</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>161,76</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>159,72</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>159,61</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>153,29</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>140.7537734890551</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>136.2779081110076</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>138.2687344768354</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>139.0028138911899</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>140.6756760173443</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>136.6560666426615</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>137.6289694731827</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>136.732936519605</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>140.7160146257081</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>136.4655441533912</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>137.9498425564219</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>137.9260020684368</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>163,49; 165,95</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>160,34; 163,6</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>159,75; 163,12</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>152,84; 157,63</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>157,62; 159,57</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>155,79; 158,5</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>156,17; 158,78</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>148,21; 152,83</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>160,94; 162,58</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>158,55; 160,77</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>158,55; 160,62</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>151,68; 154,96</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>139.0457380354457</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>134.3757863212516</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>136.8135391200294</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>135.9926503872822</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>138.9255283356854</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>134.9340388845361</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>136.1194993168702</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>134.1526089514774</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>139.5408880590095</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>135.2433819460982</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>136.8793022207905</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>135.9983435697272</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>142.4041672221276</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>137.9081752615779</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>139.5842337023151</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>141.4184983236338</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>142.3093630803251</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>138.4087740513233</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>139.182366644967</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>139.2670182761171</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>141.7865356119689</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>137.7207931522041</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>138.8863864350831</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>139.6470245425193</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>164.6288455166322</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>162.0372964017462</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>161.5871233464497</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>155.3736038145742</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>158.7206643598956</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>157.2907753250338</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>157.6002403349406</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>150.862768879968</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>161.7596016590647</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>159.715483804915</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>159.6061941613984</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>153.2891989266757</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>163.4877767370963</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>160.3393438579382</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>159.752202395582</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>152.8383933298642</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>157.6227843750401</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>155.7916490917236</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>156.1657111808528</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>148.2111981240642</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>160.9448006737371</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>158.5546758741296</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>158.5468289447721</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>151.67802057441</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>165.9480176645561</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>163.6033854255021</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>163.124428338856</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>157.6342955288679</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>159.5696838394782</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>158.4976827788194</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>158.780814985978</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>152.825523737851</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>162.5754971994357</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>160.7707022764563</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>160.6240399176602</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>154.9622693013831</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>127,6</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>122,81</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>124,47</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>137,89</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>126,08</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>121,45</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>123,11</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>134,06</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>126,86</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>122,15</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>123,81</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>136,09</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>125,69; 129,42</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>120,6; 124,97</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>122,47; 126,53</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>135,81; 140,04</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>124,21; 128,03</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>119,23; 123,39</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>121,04; 125,13</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>132,4; 135,87</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>125,5; 128,29</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>120,65; 123,68</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>122,35; 125,16</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>134,74; 137,44</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>127.6017142499947</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>122.8082641514343</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>124.4699673129261</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>137.8890378198919</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>126.0817349585735</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>121.451920198091</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>123.1076750004209</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>134.0592977758161</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>126.8636054164643</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>122.147561154295</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>123.8076008298541</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>136.0873286923118</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>125.692400831572</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>120.5973789900827</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>122.4716574692994</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>135.8101720034165</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>124.2082189124435</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>119.2276281825091</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>121.0442523413011</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>132.4042399224872</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>125.504495408449</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>120.6481000779833</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>122.3508589096817</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>134.7375526166087</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>129.4201798362878</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>124.9701962895935</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>126.5275194843106</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>140.0382938452524</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>128.0270864039212</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>123.3851391296335</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>125.1316997948789</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>135.8716835821866</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>128.2946685045747</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>123.6840150480085</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>125.1572965178322</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>137.4425700959613</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1344,15 +1329,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
